--- a/backend/pruebas/plantilla-funcionarios-academicos.xlsx
+++ b/backend/pruebas/plantilla-funcionarios-academicos.xlsx
@@ -53,7 +53,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dependencia</t>
+          <t xml:space="preserve">cargo</t>
         </is>
       </c>
     </row>
@@ -100,7 +100,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Division de Admisiones, Registro y Control Academico</t>
+          <t xml:space="preserve">Tecnico Administrativo de Procesos Academicos</t>
         </is>
       </c>
     </row>
@@ -147,7 +147,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secretaria General FIET</t>
+          <t xml:space="preserve">Profesional de Apoyo Academico</t>
         </is>
       </c>
     </row>
